--- a/static/excel/HCA_model.xlsx
+++ b/static/excel/HCA_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Cover" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="P&amp;L" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Balance Sheet" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Cash Flow" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Ratios &amp; FCF" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Segments" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="WACC" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="DCF" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Scorecard" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cover" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="P&amp;L" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balance Sheet" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash Flow" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ratios &amp; FCF" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Segments" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WACC" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DCF" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scorecard" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -216,13 +216,13 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="001B5E20"/>
+      <color rgb="001565C0"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="001565C0"/>
+      <color rgb="001B5E20"/>
       <sz val="10"/>
     </font>
     <font>
@@ -242,7 +242,7 @@
       <sz val="8"/>
     </font>
   </fonts>
-  <fills count="20">
+  <fills count="19">
     <fill>
       <patternFill/>
     </fill>
@@ -326,11 +326,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF9C4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00BBDEFB"/>
       </patternFill>
     </fill>
@@ -366,7 +361,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="143">
+  <cellXfs count="135">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -714,30 +709,6 @@
     <xf numFmtId="0" fontId="27" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="6" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="6" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -750,7 +721,7 @@
     <xf numFmtId="0" fontId="29" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="30" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="3" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -762,10 +733,10 @@
     <xf numFmtId="0" fontId="13" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="31" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="32" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -7339,11 +7310,11 @@
         </is>
       </c>
       <c r="B5" s="43" t="n">
-        <v>95990.16800000001</v>
+        <v>87420.48880000001</v>
       </c>
       <c r="C5" s="44" t="inlineStr">
         <is>
-          <t>FMP marketCap  |  price $432.7</t>
+          <t>FMP marketCap  |  price $394.07</t>
         </is>
       </c>
     </row>
@@ -7425,11 +7396,11 @@
         </is>
       </c>
       <c r="B12" s="46" t="n">
-        <v>0.0446</v>
+        <v>0.0457</v>
       </c>
       <c r="C12" s="44" t="inlineStr">
         <is>
-          <t>FRED series DGS10  |  latest: 2026-05-13</t>
+          <t>FRED series DGS10  |  latest: 2026-05-21</t>
         </is>
       </c>
     </row>
@@ -7440,7 +7411,7 @@
         </is>
       </c>
       <c r="B13" s="48" t="n">
-        <v>0.0446</v>
+        <v>0.0457</v>
       </c>
       <c r="C13" s="49" t="inlineStr">
         <is>
@@ -7508,11 +7479,11 @@
     <row r="19">
       <c r="A19" s="17" t="inlineStr">
         <is>
-          <t>Damodaran re-levered  (D/E = 0.50x,  t = 20.9%)</t>
+          <t>Damodaran re-levered  (D/E = 0.55x,  t = 20.9%)</t>
         </is>
       </c>
       <c r="B19" s="50" t="n">
-        <v>1.399</v>
+        <v>1.438</v>
       </c>
       <c r="C19" s="44">
         <f> unlevered × (1 + (1 − t) × D/E)</f>
@@ -7526,7 +7497,7 @@
         </is>
       </c>
       <c r="B20" s="51" t="n">
-        <v>1.239</v>
+        <v>1.252</v>
       </c>
       <c r="C20" s="49" t="inlineStr">
         <is>
@@ -7700,11 +7671,11 @@
         </is>
       </c>
       <c r="B35" s="46" t="n">
-        <v>0.0578</v>
+        <v>0.05890000000000001</v>
       </c>
       <c r="C35" s="44" t="inlineStr">
         <is>
-          <t>Rf 4.46% + spread 1.32%</t>
+          <t>Rf 4.57% + spread 1.32%</t>
         </is>
       </c>
     </row>
@@ -7730,7 +7701,7 @@
         </is>
       </c>
       <c r="B37" s="48" t="n">
-        <v>0.0535</v>
+        <v>0.0541</v>
       </c>
       <c r="C37" s="49" t="inlineStr">
         <is>
@@ -7795,16 +7766,16 @@
     <row r="44" ht="22" customHeight="1">
       <c r="A44" s="54" t="inlineStr">
         <is>
-          <t>WACC  =  (E/V × Re)  +  (D/V × Rd × (1 − t))</t>
+          <t>WACC  =  MAX(8.5%, (E/V × Re) + (D/V × Rd × (1 − t)))</t>
         </is>
       </c>
       <c r="B44" s="55">
-        <f>B8*B28+B9*B37*(1-B41)</f>
+        <f>MAX(0.085, B8*B28+B9*B37*(1-B41))</f>
         <v/>
       </c>
       <c r="C44" s="56" t="inlineStr">
         <is>
-          <t>Used as discount rate in DCF tab</t>
+          <t>Floored 8.5% (D-001); raw formula below</t>
         </is>
       </c>
     </row>
@@ -8167,13 +8138,13 @@
         <v/>
       </c>
       <c r="G7" s="71" t="n">
-        <v>0.0388</v>
+        <v>0.0387</v>
       </c>
       <c r="H7" s="71" t="n">
-        <v>0.0482</v>
+        <v>0.0485</v>
       </c>
       <c r="I7" s="71" t="n">
-        <v>0.0543</v>
+        <v>0.0545</v>
       </c>
       <c r="J7" s="72">
         <f>I7</f>
@@ -8517,13 +8488,13 @@
         <v/>
       </c>
       <c r="G15" s="77" t="n">
-        <v>78532.89999999999</v>
+        <v>78527.7</v>
       </c>
       <c r="H15" s="77" t="n">
-        <v>82321.60000000001</v>
+        <v>82339</v>
       </c>
       <c r="I15" s="77" t="n">
-        <v>86788.7</v>
+        <v>86825.7</v>
       </c>
       <c r="J15" s="78">
         <f>I15*(1+J7)</f>
@@ -8551,27 +8522,27 @@
       </c>
       <c r="G16" s="82" t="inlineStr">
         <is>
-          <t>77,101 — 79,795</t>
+          <t>77,086 — 79,779</t>
         </is>
       </c>
       <c r="H16" s="82" t="inlineStr">
         <is>
-          <t>81,459 — 83,977</t>
+          <t>81,486 — 84,005</t>
         </is>
       </c>
       <c r="I16" s="82" t="inlineStr">
         <is>
-          <t>86,691 — 86,887</t>
+          <t>86,746 — 86,906</t>
         </is>
       </c>
       <c r="J16" s="82" t="inlineStr">
         <is>
-          <t>90,686 — 93,802</t>
+          <t>90,754 — 93,872</t>
         </is>
       </c>
       <c r="K16" s="82" t="inlineStr">
         <is>
-          <t>98,248 — 101,624</t>
+          <t>97,113 — 100,450</t>
         </is>
       </c>
       <c r="L16" s="83" t="inlineStr">
@@ -8598,13 +8569,13 @@
         <v>18</v>
       </c>
       <c r="I17" s="84" t="n">
-        <v>10</v>
-      </c>
-      <c r="J17" s="85" t="n">
-        <v>5</v>
+        <v>12</v>
+      </c>
+      <c r="J17" s="84" t="n">
+        <v>11</v>
       </c>
       <c r="K17" s="85" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L17" s="83" t="inlineStr">
         <is>
@@ -8715,13 +8686,13 @@
         <v/>
       </c>
       <c r="G20" s="77" t="n">
-        <v>16684.1</v>
+        <v>16683</v>
       </c>
       <c r="H20" s="77" t="n">
-        <v>17489</v>
+        <v>17492.7</v>
       </c>
       <c r="I20" s="77" t="n">
-        <v>18438</v>
+        <v>18445.8</v>
       </c>
       <c r="J20" s="78">
         <f>J15*J8</f>
@@ -8749,27 +8720,27 @@
       </c>
       <c r="G21" s="82" t="inlineStr">
         <is>
-          <t>16,380 — 16,952</t>
+          <t>16,377 — 16,949</t>
         </is>
       </c>
       <c r="H21" s="82" t="inlineStr">
         <is>
-          <t>17,306 — 17,841</t>
+          <t>17,311 — 17,847</t>
         </is>
       </c>
       <c r="I21" s="82" t="inlineStr">
         <is>
-          <t>18,417 — 18,459</t>
+          <t>18,429 — 18,463</t>
         </is>
       </c>
       <c r="J21" s="82" t="inlineStr">
         <is>
-          <t>19,266 — 19,928</t>
+          <t>19,280 — 19,943</t>
         </is>
       </c>
       <c r="K21" s="82" t="inlineStr">
         <is>
-          <t>20,872 — 21,590</t>
+          <t>20,631 — 21,340</t>
         </is>
       </c>
       <c r="L21" s="83" t="inlineStr">
@@ -9949,7 +9920,7 @@
         </is>
       </c>
       <c r="B61" s="112" t="n">
-        <v>432.7</v>
+        <v>394.07</v>
       </c>
       <c r="C61" s="104" t="n"/>
       <c r="D61" s="104" t="n"/>
@@ -10049,7 +10020,7 @@
     <row r="1" ht="18" customHeight="1">
       <c r="A1" s="114" t="inlineStr">
         <is>
-          <t>JS SCORECARD — HCA  |  Master Prompt v2  |  15 May 2026  |  Sector bucket: Stable Compounder</t>
+          <t>JS SCORECARD — HCA  |  Master Prompt v2  |  25 May 2026  |  Sector bucket: Stable Compounder</t>
         </is>
       </c>
     </row>
@@ -10152,10 +10123,14 @@
       </c>
       <c r="D8" s="122" t="inlineStr">
         <is>
-          <t>— user input required</t>
-        </is>
-      </c>
-      <c r="E8" s="123" t="n"/>
+          <t>User-supplied via web form</t>
+        </is>
+      </c>
+      <c r="E8" s="123" t="inlineStr">
+        <is>
+          <t>MOD-HIGH</t>
+        </is>
+      </c>
       <c r="F8" s="124">
         <f>IF(E8="HIGH",10,IF(E8="MOD-HIGH",7,IF(E8="MOD-LOW",3,IF(E8="LOW",0,""))))</f>
         <v/>
@@ -10164,42 +10139,46 @@
         <f>IF(F8="",0,C8*F8*10)</f>
         <v/>
       </c>
-      <c r="H8" s="126" t="inlineStr"/>
+      <c r="H8" s="126" t="inlineStr">
+        <is>
+          <t>User-supplied via web form</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="127" t="inlineStr">
+      <c r="A9" s="119" t="inlineStr">
         <is>
           <t xml:space="preserve">  Moat Profile</t>
         </is>
       </c>
-      <c r="B9" s="128" t="inlineStr">
+      <c r="B9" s="120" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="C9" s="129" t="n">
+      <c r="C9" s="121" t="n">
         <v>0.1</v>
       </c>
-      <c r="D9" s="130" t="inlineStr">
-        <is>
-          <t>GM 41.5% ✓ (&gt;40%)  |  GM trend +3.0% ✓ (&gt;+1pp)  |  ROIC-WACC +19.0% ✓ (&gt;+5pp)  |  Rev consistency σ=2.4% ✓ (&lt;8%)  [4/4 indicators positive — proxy score]</t>
-        </is>
-      </c>
-      <c r="E9" s="131" t="inlineStr">
+      <c r="D9" s="122" t="inlineStr">
+        <is>
+          <t>GM 41.5% ✓ (&gt;40%)  |  GM trend +3.0% ✓ (&gt;+1pp)  |  ROIC-WACC +15.4% ✓ (&gt;+5pp)  |  Rev consistency σ=2.4% ✓ (&lt;8%)  [4/4 indicators positive — proxy score]</t>
+        </is>
+      </c>
+      <c r="E9" s="127" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="F9" s="132" t="n">
+      <c r="F9" s="124" t="n">
         <v>10</v>
       </c>
-      <c r="G9" s="133">
+      <c r="G9" s="125">
         <f>IF(F9="",0,C9*F9*10)</f>
         <v/>
       </c>
-      <c r="H9" s="134" t="inlineStr">
-        <is>
-          <t>GM 41.5% ✓ (&gt;40%)  |  GM trend +3.0% ✓ (&gt;+1pp)  |  ROIC-WACC +19.0% ✓ (&gt;+5pp)  |  Rev consistency σ=2.4% ✓ (&lt;8%)  [4/4 indicators positive — proxy score]</t>
+      <c r="H9" s="126" t="inlineStr">
+        <is>
+          <t>GM 41.5% ✓ (&gt;40%)  |  GM trend +3.0% ✓ (&gt;+1pp)  |  ROIC-WACC +15.4% ✓ (&gt;+5pp)  |  Rev consistency σ=2.4% ✓ (&lt;8%)  [4/4 indicators positive — proxy score]</t>
         </is>
       </c>
     </row>
@@ -10219,10 +10198,14 @@
       </c>
       <c r="D10" s="122" t="inlineStr">
         <is>
-          <t>— user input required</t>
-        </is>
-      </c>
-      <c r="E10" s="123" t="n"/>
+          <t>User-supplied via web form</t>
+        </is>
+      </c>
+      <c r="E10" s="123" t="inlineStr">
+        <is>
+          <t>MOD-HIGH</t>
+        </is>
+      </c>
       <c r="F10" s="124">
         <f>IF(E10="HIGH",10,IF(E10="MOD-HIGH",7,IF(E10="MOD-LOW",3,IF(E10="LOW",0,""))))</f>
         <v/>
@@ -10231,42 +10214,46 @@
         <f>IF(F10="",0,C10*F10*10)</f>
         <v/>
       </c>
-      <c r="H10" s="126" t="inlineStr"/>
+      <c r="H10" s="126" t="inlineStr">
+        <is>
+          <t>User-supplied via web form</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="127" t="inlineStr">
+      <c r="A11" s="119" t="inlineStr">
         <is>
           <t xml:space="preserve">  Management</t>
         </is>
       </c>
-      <c r="B11" s="128" t="inlineStr">
+      <c r="B11" s="120" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="C11" s="129" t="n">
+      <c r="C11" s="121" t="n">
         <v>0.075</v>
       </c>
-      <c r="D11" s="130" t="inlineStr">
-        <is>
-          <t>ROIC trend +1.6% ✓ (≥-2pp)  |  GM maintained +3.0% ✓  |  Op margin +0.8% ✓ (≥-2pp)  |  Capital returns MOD-LOW ✗  |  Share count -8.1%/yr ✓ (net buyback)  [4/5 indicators positive — proxy score]</t>
-        </is>
-      </c>
-      <c r="E11" s="135" t="inlineStr">
+      <c r="D11" s="122" t="inlineStr">
+        <is>
+          <t>ROIC trend +1.6% ✓ (&gt;=-2pp)  |  GM maintained +3.0% ✓  |  Op margin +0.8% ✓ (≥-2pp)  |  Capital returns MOD-LOW ✗  |  Share count -8.1%/yr ✓ (net buyback)  [4/5 indicators positive — proxy score]</t>
+        </is>
+      </c>
+      <c r="E11" s="123" t="inlineStr">
         <is>
           <t>MOD-HIGH</t>
         </is>
       </c>
-      <c r="F11" s="132" t="n">
+      <c r="F11" s="124" t="n">
         <v>8</v>
       </c>
-      <c r="G11" s="133">
+      <c r="G11" s="125">
         <f>IF(F11="",0,C11*F11*10)</f>
         <v/>
       </c>
-      <c r="H11" s="134" t="inlineStr">
-        <is>
-          <t>ROIC trend +1.6% ✓ (≥-2pp)  |  GM maintained +3.0% ✓  |  Op margin +0.8% ✓ (≥-2pp)  |  Capital returns MOD-LOW ✗  |  Share count -8.1%/yr ✓ (net buyback)  [4/5 indicators positive — proxy score]</t>
+      <c r="H11" s="126" t="inlineStr">
+        <is>
+          <t>ROIC trend +1.6% ✓ (&gt;=-2pp)  |  GM maintained +3.0% ✓  |  Op margin +0.8% ✓ (≥-2pp)  |  Capital returns MOD-LOW ✗  |  Share count -8.1%/yr ✓ (net buyback)  [4/5 indicators positive — proxy score]</t>
         </is>
       </c>
     </row>
@@ -10278,148 +10265,148 @@
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="127" t="inlineStr">
+      <c r="A13" s="119" t="inlineStr">
         <is>
           <t xml:space="preserve">  Revenue 3yr CAGR</t>
         </is>
       </c>
-      <c r="B13" s="128" t="inlineStr">
+      <c r="B13" s="120" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="C13" s="129" t="n">
+      <c r="C13" s="121" t="n">
         <v>0.1</v>
       </c>
-      <c r="D13" s="130" t="inlineStr">
+      <c r="D13" s="122" t="inlineStr">
         <is>
           <t>7.9%</t>
         </is>
       </c>
-      <c r="E13" s="135" t="inlineStr">
+      <c r="E13" s="123" t="inlineStr">
         <is>
           <t>MOD-HIGH</t>
         </is>
       </c>
-      <c r="F13" s="132" t="n">
+      <c r="F13" s="124" t="n">
         <v>9.869999999999999</v>
       </c>
-      <c r="G13" s="133">
+      <c r="G13" s="125">
         <f>IF(F13="",0,C13*F13*10)</f>
         <v/>
       </c>
-      <c r="H13" s="134" t="inlineStr">
+      <c r="H13" s="126" t="inlineStr">
         <is>
           <t>7.9%</t>
         </is>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="127" t="inlineStr">
+      <c r="A14" s="119" t="inlineStr">
         <is>
           <t xml:space="preserve">  Cash Quality  (FCF / Net Income)</t>
         </is>
       </c>
-      <c r="B14" s="128" t="inlineStr">
+      <c r="B14" s="120" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="C14" s="129" t="n">
+      <c r="C14" s="121" t="n">
         <v>0.1</v>
       </c>
-      <c r="D14" s="130" t="inlineStr">
+      <c r="D14" s="122" t="inlineStr">
         <is>
           <t>106%  [through-cycle: 70/30 latest+5yr median, latest 113.4% → smoothed 106.2%]</t>
         </is>
       </c>
-      <c r="E14" s="131" t="inlineStr">
+      <c r="E14" s="127" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="F14" s="132" t="n">
-        <v>12</v>
-      </c>
-      <c r="G14" s="133">
+      <c r="F14" s="124" t="n">
+        <v>10</v>
+      </c>
+      <c r="G14" s="125">
         <f>IF(F14="",0,C14*F14*10)</f>
         <v/>
       </c>
-      <c r="H14" s="134" t="inlineStr">
+      <c r="H14" s="126" t="inlineStr">
         <is>
           <t>106%  [through-cycle: 70/30 latest+5yr median, latest 113.4% → smoothed 106.2%]</t>
         </is>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="127" t="inlineStr">
+      <c r="A15" s="119" t="inlineStr">
         <is>
           <t xml:space="preserve">  Capital Returns</t>
         </is>
       </c>
-      <c r="B15" s="128" t="inlineStr">
+      <c r="B15" s="120" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="C15" s="129" t="n">
+      <c r="C15" s="121" t="n">
         <v>0.05</v>
       </c>
-      <c r="D15" s="130" t="inlineStr">
+      <c r="D15" s="122" t="inlineStr">
         <is>
           <t>$10,067mm latest FY — debt-funded  [payout 131% of FCF — &gt; 100%, unsustainable]</t>
         </is>
       </c>
-      <c r="E15" s="136" t="inlineStr">
+      <c r="E15" s="128" t="inlineStr">
         <is>
           <t>MOD-LOW</t>
         </is>
       </c>
-      <c r="F15" s="132" t="n">
+      <c r="F15" s="124" t="n">
         <v>0.5</v>
       </c>
-      <c r="G15" s="133">
+      <c r="G15" s="125">
         <f>IF(F15="",0,C15*F15*10)</f>
         <v/>
       </c>
-      <c r="H15" s="134" t="inlineStr">
+      <c r="H15" s="126" t="inlineStr">
         <is>
           <t>$10,067mm latest FY — debt-funded  [payout 131% of FCF — &gt; 100%, unsustainable]</t>
         </is>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="127" t="inlineStr">
+      <c r="A16" s="119" t="inlineStr">
         <is>
           <t xml:space="preserve">  ROIC</t>
         </is>
       </c>
-      <c r="B16" s="128" t="inlineStr">
+      <c r="B16" s="120" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="C16" s="129" t="n">
+      <c r="C16" s="121" t="n">
         <v>0.075</v>
       </c>
-      <c r="D16" s="130" t="inlineStr">
+      <c r="D16" s="122" t="inlineStr">
         <is>
           <t>22.5%</t>
         </is>
       </c>
-      <c r="E16" s="131" t="inlineStr">
+      <c r="E16" s="127" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="F16" s="132" t="n">
-        <v>10.92</v>
-      </c>
-      <c r="G16" s="133">
+      <c r="F16" s="124" t="n">
+        <v>10</v>
+      </c>
+      <c r="G16" s="125">
         <f>IF(F16="",0,C16*F16*10)</f>
         <v/>
       </c>
-      <c r="H16" s="134" t="inlineStr">
+      <c r="H16" s="126" t="inlineStr">
         <is>
           <t>22.5%</t>
         </is>
@@ -10433,113 +10420,113 @@
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="127" t="inlineStr">
+      <c r="A18" s="119" t="inlineStr">
         <is>
           <t xml:space="preserve">  Credit Risk  (D / EBITDA)</t>
         </is>
       </c>
-      <c r="B18" s="128" t="inlineStr">
+      <c r="B18" s="120" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="C18" s="129" t="n">
+      <c r="C18" s="121" t="n">
         <v>0.05</v>
       </c>
-      <c r="D18" s="130" t="inlineStr">
+      <c r="D18" s="122" t="inlineStr">
         <is>
           <t>3.1x</t>
         </is>
       </c>
-      <c r="E18" s="136" t="inlineStr">
+      <c r="E18" s="128" t="inlineStr">
         <is>
           <t>MOD-LOW</t>
         </is>
       </c>
-      <c r="F18" s="132" t="n">
+      <c r="F18" s="124" t="n">
         <v>6.74</v>
       </c>
-      <c r="G18" s="133">
+      <c r="G18" s="125">
         <f>IF(F18="",0,C18*F18*10)</f>
         <v/>
       </c>
-      <c r="H18" s="134" t="inlineStr">
+      <c r="H18" s="126" t="inlineStr">
         <is>
           <t>3.1x</t>
         </is>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="127" t="inlineStr">
+      <c r="A19" s="119" t="inlineStr">
         <is>
           <t xml:space="preserve">  Interest Cover  (EBIT / Interest)</t>
         </is>
       </c>
-      <c r="B19" s="128" t="inlineStr">
+      <c r="B19" s="120" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="C19" s="129" t="n">
+      <c r="C19" s="121" t="n">
         <v>0.075</v>
       </c>
-      <c r="D19" s="130" t="inlineStr">
+      <c r="D19" s="122" t="inlineStr">
         <is>
           <t>5.3x</t>
         </is>
       </c>
-      <c r="E19" s="135" t="inlineStr">
+      <c r="E19" s="123" t="inlineStr">
         <is>
           <t>MOD-HIGH</t>
         </is>
       </c>
-      <c r="F19" s="132" t="n">
+      <c r="F19" s="124" t="n">
         <v>7.66</v>
       </c>
-      <c r="G19" s="133">
+      <c r="G19" s="125">
         <f>IF(F19="",0,C19*F19*10)</f>
         <v/>
       </c>
-      <c r="H19" s="134" t="inlineStr">
+      <c r="H19" s="126" t="inlineStr">
         <is>
           <t>5.3x</t>
         </is>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="127" t="inlineStr">
+      <c r="A20" s="119" t="inlineStr">
         <is>
           <t xml:space="preserve">  Execution Risk</t>
         </is>
       </c>
-      <c r="B20" s="128" t="inlineStr">
+      <c r="B20" s="120" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="C20" s="129" t="n">
+      <c r="C20" s="121" t="n">
         <v>0.05</v>
       </c>
-      <c r="D20" s="130" t="inlineStr">
-        <is>
-          <t>Rev growth σ=2.4%  |  Op margin σ=0.6%  [proxy — lower σ = lower risk = higher score]</t>
-        </is>
-      </c>
-      <c r="E20" s="131" t="inlineStr">
+      <c r="D20" s="122" t="inlineStr">
+        <is>
+          <t>Rev growth σ=2.4%  |  OM trend -0.6%, σ=0.6%  [quality = direction + stability]</t>
+        </is>
+      </c>
+      <c r="E20" s="127" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="F20" s="132" t="n">
+      <c r="F20" s="124" t="n">
         <v>10</v>
       </c>
-      <c r="G20" s="133">
+      <c r="G20" s="125">
         <f>IF(F20="",0,C20*F20*10)</f>
         <v/>
       </c>
-      <c r="H20" s="134" t="inlineStr">
-        <is>
-          <t>Rev growth σ=2.4%  |  Op margin σ=0.6%  [proxy — lower σ = lower risk = higher score]</t>
+      <c r="H20" s="126" t="inlineStr">
+        <is>
+          <t>Rev growth σ=2.4%  |  OM trend -0.6%, σ=0.6%  [quality = direction + stability]</t>
         </is>
       </c>
     </row>
@@ -10551,76 +10538,76 @@
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="127" t="inlineStr">
+      <c r="A22" s="119" t="inlineStr">
         <is>
           <t xml:space="preserve">  Valuation vs Median  (P/E)</t>
         </is>
       </c>
-      <c r="B22" s="128" t="inlineStr">
+      <c r="B22" s="120" t="inlineStr">
         <is>
           <t>P4</t>
         </is>
       </c>
-      <c r="C22" s="129" t="n">
+      <c r="C22" s="121" t="n">
         <v>0.1</v>
       </c>
-      <c r="D22" s="130" t="inlineStr">
-        <is>
-          <t>Current 15.9x  |  5yr avg 13.5x  |  DCF-implied 19.5x  [+18% vs benchmark]</t>
-        </is>
-      </c>
-      <c r="E22" s="136" t="inlineStr">
+      <c r="D22" s="122" t="inlineStr">
+        <is>
+          <t>Current 15.9x  |  5yr avg 13.5x  |  DCF-implied 17.5x [ref only — not used as benchmark]  [+18% vs benchmark]  [trail=4.16 | fwd_pe=13.0x→7.56 | abs=10.0 → blended 40/40/20=6.68]  PEG=461.04 (fwd_pe=13.0x / eps_growth=3%)</t>
+        </is>
+      </c>
+      <c r="E22" s="128" t="inlineStr">
         <is>
           <t>MOD-LOW</t>
         </is>
       </c>
-      <c r="F22" s="132" t="n">
-        <v>4.16</v>
-      </c>
-      <c r="G22" s="133">
+      <c r="F22" s="124" t="n">
+        <v>6.68</v>
+      </c>
+      <c r="G22" s="125">
         <f>IF(F22="",0,C22*F22*10)</f>
         <v/>
       </c>
-      <c r="H22" s="134" t="inlineStr">
-        <is>
-          <t>Current 15.9x  |  5yr avg 13.5x  |  DCF-implied 19.5x  [+18% vs benchmark]</t>
+      <c r="H22" s="126" t="inlineStr">
+        <is>
+          <t>Current 15.9x  |  5yr avg 13.5x  |  DCF-implied 17.5x [ref only — not used as benchmark]  [+18% vs benchmark]  [trail=4.16 | fwd_pe=13.0x→7.56 | abs=10.0 → blended 40/40/20=6.68]  PEG=461.04 (fwd_pe=13.0x / eps_growth=3%)</t>
         </is>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="127" t="inlineStr">
+      <c r="A23" s="119" t="inlineStr">
         <is>
           <t xml:space="preserve">  Valuation vs Median  (P/FCF)</t>
         </is>
       </c>
-      <c r="B23" s="128" t="inlineStr">
+      <c r="B23" s="120" t="inlineStr">
         <is>
           <t>P4</t>
         </is>
       </c>
-      <c r="C23" s="129" t="n">
+      <c r="C23" s="121" t="n">
         <v>0.1</v>
       </c>
-      <c r="D23" s="130" t="inlineStr">
-        <is>
-          <t>Current 14.0x  |  5yr avg 15.2x  |  DCF-implied 17.2x  [-8% vs benchmark]</t>
-        </is>
-      </c>
-      <c r="E23" s="135" t="inlineStr">
+      <c r="D23" s="122" t="inlineStr">
+        <is>
+          <t>Current 14.0x  |  5yr avg 15.2x  |  DCF-implied 15.4x [ref only — not used as benchmark]  [-8% vs benchmark]  [trail=8.18 | fwd_pfcf=11.4x→10.00 | abs=12.0 → blended 40/40/20=9.67]  [fcf_yield=7.1% vs rf=4.6%  spread=+2.6%→modifier=+0.25]</t>
+        </is>
+      </c>
+      <c r="E23" s="123" t="inlineStr">
         <is>
           <t>MOD-HIGH</t>
         </is>
       </c>
-      <c r="F23" s="132" t="n">
-        <v>8.18</v>
-      </c>
-      <c r="G23" s="133">
+      <c r="F23" s="124" t="n">
+        <v>9.92</v>
+      </c>
+      <c r="G23" s="125">
         <f>IF(F23="",0,C23*F23*10)</f>
         <v/>
       </c>
-      <c r="H23" s="134" t="inlineStr">
-        <is>
-          <t>Current 14.0x  |  5yr avg 15.2x  |  DCF-implied 17.2x  [-8% vs benchmark]</t>
+      <c r="H23" s="126" t="inlineStr">
+        <is>
+          <t>Current 14.0x  |  5yr avg 15.2x  |  DCF-implied 15.4x [ref only — not used as benchmark]  [-8% vs benchmark]  [trail=8.18 | fwd_pfcf=11.4x→10.00 | abs=12.0 → blended 40/40/20=9.67]  [fcf_yield=7.1% vs rf=4.6%  spread=+2.6%→modifier=+0.25]</t>
         </is>
       </c>
     </row>
@@ -10635,21 +10622,21 @@
       <c r="H24" s="42" t="n"/>
     </row>
     <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="137" t="inlineStr">
+      <c r="A25" s="129" t="inlineStr">
         <is>
           <t>TOTAL SCORE  (max = 100.0)</t>
         </is>
       </c>
-      <c r="B25" s="138" t="n"/>
-      <c r="C25" s="138" t="n"/>
-      <c r="D25" s="138" t="n"/>
-      <c r="E25" s="138" t="n"/>
-      <c r="F25" s="138" t="n"/>
-      <c r="G25" s="139">
+      <c r="B25" s="130" t="n"/>
+      <c r="C25" s="130" t="n"/>
+      <c r="D25" s="130" t="n"/>
+      <c r="E25" s="130" t="n"/>
+      <c r="F25" s="130" t="n"/>
+      <c r="G25" s="131">
         <f>G8+G9+G10+G11+G13+G14+G15+G16+G18+G19+G20+G22+G23</f>
         <v/>
       </c>
-      <c r="H25" s="140" t="inlineStr">
+      <c r="H25" s="132" t="inlineStr">
         <is>
           <t>No floor cap.</t>
         </is>
@@ -10666,7 +10653,7 @@
       <c r="H26" s="42" t="n"/>
     </row>
     <row r="27" ht="24" customHeight="1">
-      <c r="A27" s="141">
+      <c r="A27" s="133">
         <f>IF(G25="","Score incomplete — fill qualitative tiers above",IF(G25&gt;=80,"STRONG BUY",IF(G25&gt;=65,"BUY",IF(G25&gt;=50,"HOLD",IF(G25&gt;=35,"REDUCE","SELL")))))</f>
         <v/>
       </c>
@@ -10682,7 +10669,7 @@
       <c r="H28" s="42" t="n"/>
     </row>
     <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="142" t="inlineStr">
+      <c r="A29" s="134" t="inlineStr">
         <is>
           <t>SCORING GUIDE:  ≥80 STRONG BUY  |  65–79 BUY  |  50–64 HOLD  |  35–49 REDUCE  |  &lt;35 SELL    ||  Soft cap (non-banks only): −5pts per 1.0x of D/EBITDA above 3.0x; −4pts per 1.0x of EBIT/Int below 3.0x; min 40    ||  Banks: gates exempt; P3 uses Equity/Assets (CET1 proxy) instead of D/EBITDA</t>
         </is>

--- a/static/excel/HCA_model.xlsx
+++ b/static/excel/HCA_model.xlsx
@@ -7396,11 +7396,11 @@
         </is>
       </c>
       <c r="B12" s="46" t="n">
-        <v>0.0457</v>
+        <v>0.04559999999999999</v>
       </c>
       <c r="C12" s="44" t="inlineStr">
         <is>
-          <t>FRED series DGS10  |  latest: 2026-05-21</t>
+          <t>FRED series DGS10  |  latest: 2026-05-22</t>
         </is>
       </c>
     </row>
@@ -7411,7 +7411,7 @@
         </is>
       </c>
       <c r="B13" s="48" t="n">
-        <v>0.0457</v>
+        <v>0.0456</v>
       </c>
       <c r="C13" s="49" t="inlineStr">
         <is>
@@ -7610,25 +7610,27 @@
       </c>
       <c r="B31" s="53" t="inlineStr">
         <is>
-          <t>Not available</t>
+          <t>BB+</t>
         </is>
       </c>
       <c r="C31" s="44" t="inlineStr">
         <is>
-          <t>FMP /ratings endpoint</t>
+          <t>User input</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="17" t="inlineStr">
         <is>
-          <t>FRED matched yield</t>
-        </is>
-      </c>
-      <c r="B32" s="53" t="n"/>
+          <t>FRED matched yield  (rating-tier index)</t>
+        </is>
+      </c>
+      <c r="B32" s="46" t="n">
+        <v>0.0698</v>
+      </c>
       <c r="C32" s="44" t="inlineStr">
         <is>
-          <t>No rating returned — FRED method not applicable</t>
+          <t>FRED BAMLH0A0HYM2EY — High Yield</t>
         </is>
       </c>
     </row>
@@ -7671,11 +7673,11 @@
         </is>
       </c>
       <c r="B35" s="46" t="n">
-        <v>0.05890000000000001</v>
+        <v>0.05879999999999999</v>
       </c>
       <c r="C35" s="44" t="inlineStr">
         <is>
-          <t>Rf 4.57% + spread 1.32%</t>
+          <t>Rf 4.56% + spread 1.32%</t>
         </is>
       </c>
     </row>
@@ -7701,11 +7703,11 @@
         </is>
       </c>
       <c r="B37" s="48" t="n">
-        <v>0.0541</v>
+        <v>0.0593</v>
       </c>
       <c r="C37" s="49" t="inlineStr">
         <is>
-          <t>Default = average of 2 source(s) above — override freely</t>
+          <t>Default = average of 3 source(s) above — override freely</t>
         </is>
       </c>
     </row>
@@ -10020,7 +10022,7 @@
     <row r="1" ht="18" customHeight="1">
       <c r="A1" s="114" t="inlineStr">
         <is>
-          <t>JS SCORECARD — HCA  |  Master Prompt v2  |  25 May 2026  |  Sector bucket: Stable Compounder</t>
+          <t>JS SCORECARD — HCA  |  Master Prompt v2  |  27 May 2026  |  Sector bucket: Stable Compounder</t>
         </is>
       </c>
     </row>
@@ -10553,16 +10555,16 @@
       </c>
       <c r="D22" s="122" t="inlineStr">
         <is>
-          <t>Current 15.9x  |  5yr avg 13.5x  |  DCF-implied 17.5x [ref only — not used as benchmark]  [+18% vs benchmark]  [trail=4.16 | fwd_pe=13.0x→7.56 | abs=10.0 → blended 40/40/20=6.68]  PEG=461.04 (fwd_pe=13.0x / eps_growth=3%)</t>
-        </is>
-      </c>
-      <c r="E22" s="128" t="inlineStr">
-        <is>
-          <t>MOD-LOW</t>
+          <t>Fwd P/E 13.0x (scoring basis)  |  5yr avg 14.0x  |  DCF-implied 17.5x [ref only — not used as benchmark]  [-7% vs benchmark]  [trail=8.07 | fwd_pe=13.0x→8.07 | abs=12.0 → blended 40/40/20=8.86]  PEG=461.04 (fwd_pe=13.0x / eps_growth=3%)</t>
+        </is>
+      </c>
+      <c r="E22" s="123" t="inlineStr">
+        <is>
+          <t>MOD-HIGH</t>
         </is>
       </c>
       <c r="F22" s="124" t="n">
-        <v>6.68</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="G22" s="125">
         <f>IF(F22="",0,C22*F22*10)</f>
@@ -10570,7 +10572,7 @@
       </c>
       <c r="H22" s="126" t="inlineStr">
         <is>
-          <t>Current 15.9x  |  5yr avg 13.5x  |  DCF-implied 17.5x [ref only — not used as benchmark]  [+18% vs benchmark]  [trail=4.16 | fwd_pe=13.0x→7.56 | abs=10.0 → blended 40/40/20=6.68]  PEG=461.04 (fwd_pe=13.0x / eps_growth=3%)</t>
+          <t>Fwd P/E 13.0x (scoring basis)  |  5yr avg 14.0x  |  DCF-implied 17.5x [ref only — not used as benchmark]  [-7% vs benchmark]  [trail=8.07 | fwd_pe=13.0x→8.07 | abs=12.0 → blended 40/40/20=8.86]  PEG=461.04 (fwd_pe=13.0x / eps_growth=3%)</t>
         </is>
       </c>
     </row>
@@ -10590,7 +10592,7 @@
       </c>
       <c r="D23" s="122" t="inlineStr">
         <is>
-          <t>Current 14.0x  |  5yr avg 15.2x  |  DCF-implied 15.4x [ref only — not used as benchmark]  [-8% vs benchmark]  [trail=8.18 | fwd_pfcf=11.4x→10.00 | abs=12.0 → blended 40/40/20=9.67]  [fcf_yield=7.1% vs rf=4.6%  spread=+2.6%→modifier=+0.25]</t>
+          <t>Current 14.0x  |  5yr avg 15.0x  |  DCF-implied 15.4x [ref only — not used as benchmark]  [-7% vs benchmark]  [trail=8.00 | fwd_pfcf=11.4x→10.00 | abs=12.0 → blended 40/40/20=9.60]  [fcf_yield=7.1% vs rf=4.6%  spread=+2.6%→modifier=+0.25]</t>
         </is>
       </c>
       <c r="E23" s="123" t="inlineStr">
@@ -10599,7 +10601,7 @@
         </is>
       </c>
       <c r="F23" s="124" t="n">
-        <v>9.92</v>
+        <v>9.85</v>
       </c>
       <c r="G23" s="125">
         <f>IF(F23="",0,C23*F23*10)</f>
@@ -10607,7 +10609,7 @@
       </c>
       <c r="H23" s="126" t="inlineStr">
         <is>
-          <t>Current 14.0x  |  5yr avg 15.2x  |  DCF-implied 15.4x [ref only — not used as benchmark]  [-8% vs benchmark]  [trail=8.18 | fwd_pfcf=11.4x→10.00 | abs=12.0 → blended 40/40/20=9.67]  [fcf_yield=7.1% vs rf=4.6%  spread=+2.6%→modifier=+0.25]</t>
+          <t>Current 14.0x  |  5yr avg 15.0x  |  DCF-implied 15.4x [ref only — not used as benchmark]  [-7% vs benchmark]  [trail=8.00 | fwd_pfcf=11.4x→10.00 | abs=12.0 → blended 40/40/20=9.60]  [fcf_yield=7.1% vs rf=4.6%  spread=+2.6%→modifier=+0.25]</t>
         </is>
       </c>
     </row>
